--- a/ZAC_zzx/results/fourway/四方法对比_论文对齐.xlsx
+++ b/ZAC_zzx/results/fourway/四方法对比_论文对齐.xlsx
@@ -564,8 +564,12 @@
           <t>bv_n14</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13</v>
+      </c>
       <c r="D3" t="n">
         <v>13</v>
       </c>
@@ -625,8 +629,12 @@
           <t>bv_n19</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C4" t="n">
+        <v>18</v>
+      </c>
       <c r="D4" t="n">
         <v>18</v>
       </c>
@@ -930,8 +938,12 @@
           <t>ghz_n23</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C9" t="n">
+        <v>22</v>
+      </c>
       <c r="D9" t="n">
         <v>22</v>
       </c>

--- a/ZAC_zzx/results/fourway/四方法对比_论文对齐.xlsx
+++ b/ZAC_zzx/results/fourway/四方法对比_论文对齐.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -452,12 +452,22 @@
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>口径：ZAC 列 = HPCA'25 原程序冻结真值（12/18 与论文逐位一致）；ICCAD 列 = 论文复现管线（opt3/u1-u2 预处理、论文参数、论文自己的 NavizEvaluator 计数；15 电路 13/15 与 Table I 步数精确一致，qft 两例 输入电路漂移；bv14/bv19/ghz23 为 Table I 外同管线补跑）；论文不报 ICCAD 保真度/时长，故无此列。遗传列 = GA初始化+鬼点硬保证层（我们的方法，仅供对照）。Table I 原值列供逐行核对。</t>
+          <t>口径：ZAC 列 = HPCA'25 原程序冻结真值（12/18 与论文逐位一致）；ICCAD 列 = **mqt.qmap 3.2.0（论文版本）**论文管线全量重采（opt3/u1-u2 预处理、论文参数、NavizEvaluator）：步数 26/30 与 Table I 精确一致（qft 两例输入电路漂移），place/route/rearr 为本机 3.2.0 实测（rearr 已换算 ms 对齐论文单位）；bv14/bv19/ghz23 为 Table I 外同管线补跑。注意 .venv_qmap 当前为 3.5.0（步数漂移 13/30），论文对齐一律用 3.2.0。论文不报 ICCAD 保真度，故无此列。遗传列 = GA初始化+鬼点硬保证层（我们的方法，仅供对照）。</t>
         </is>
       </c>
     </row>
@@ -509,50 +519,100 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ICCAD Steps(ra/agn)</t>
+          <t>ICCAD ra place_ms</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>ICCAD Steps(rw/astar)</t>
+          <t>ICCAD ra route_ms</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>ICCAD rearr ms</t>
+          <t>ICCAD ra Steps</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>ICCAD 编译s</t>
+          <t>ICCAD ra rearr_ms</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
+          <t>ICCAD rw place_ms</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>ICCAD rw route_ms</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>ICCAD rw Steps</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>ICCAD rw rearr_ms</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Table I ra_place</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Table I ra_route</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
           <t>Table I ra_steps</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Table I ra_rearr</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Table I rw_place</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Table I rw_route</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Table I rw_steps</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>Table I rw_rearr</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>遗传(无前瞻) Steps</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>遗传(前瞻) Steps</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>遗传 保真度</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>遗传 编译s</t>
         </is>
@@ -589,37 +649,79 @@
         <v>5.09</v>
       </c>
       <c r="J3" t="n">
+        <v>605</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="n">
         <v>26</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
+        <v>2.782</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3899</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
         <v>26</v>
       </c>
-      <c r="L3" t="n">
-        <v>2781.71</v>
-      </c>
-      <c r="M3" t="n">
-        <v>5.339</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="n">
+        <v>2.782</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
         <v>27</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="AA3" t="n">
         <v>27</v>
       </c>
-      <c r="R3" t="n">
+      <c r="AB3" t="n">
         <v>0.8512</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AC3" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -654,37 +756,79 @@
         <v>5.3</v>
       </c>
       <c r="J4" t="n">
+        <v>979</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" t="n">
         <v>37</v>
       </c>
-      <c r="K4" t="n">
-        <v>36</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3813.37</v>
-      </c>
       <c r="M4" t="n">
-        <v>6.867</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3.915</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5319</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
       </c>
       <c r="P4" t="n">
         <v>36</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.812</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
         <v>36</v>
       </c>
-      <c r="R4" t="n">
+      <c r="AA4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0.7938</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AC4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -719,33 +863,63 @@
         <v>3.47</v>
       </c>
       <c r="J5" t="n">
+        <v>998</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" t="n">
         <v>37</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5556</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
         <v>36</v>
       </c>
-      <c r="L5" t="n">
-        <v>4125.32</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
+        <v>4.125</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T5" t="n">
         <v>37</v>
       </c>
-      <c r="O5" t="n">
+      <c r="U5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X5" t="n">
         <v>36</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Y5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Z5" t="n">
         <v>35</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="AA5" t="n">
         <v>35</v>
       </c>
-      <c r="R5" t="n">
+      <c r="AB5" t="n">
         <v>0.776</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AC5" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -780,33 +954,63 @@
         <v>3.05</v>
       </c>
       <c r="J6" t="n">
+        <v>3193</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
         <v>73</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
+        <v>11.029</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11973</v>
+      </c>
+      <c r="O6" t="n">
+        <v>16</v>
+      </c>
+      <c r="P6" t="n">
         <v>76</v>
       </c>
-      <c r="L6" t="n">
-        <v>8452.66</v>
-      </c>
-      <c r="M6" t="n">
-        <v>11.751</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
+        <v>8.452999999999999</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T6" t="n">
         <v>73</v>
       </c>
-      <c r="O6" t="n">
+      <c r="U6" t="n">
+        <v>11</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X6" t="n">
         <v>76</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Y6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z6" t="n">
         <v>71</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="AA6" t="n">
         <v>71</v>
       </c>
-      <c r="R6" t="n">
+      <c r="AB6" t="n">
         <v>0.4656</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AC6" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -841,33 +1045,63 @@
         <v>6.56</v>
       </c>
       <c r="J7" t="n">
+        <v>999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
         <v>43</v>
       </c>
-      <c r="K7" t="n">
-        <v>42</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4491.71</v>
-      </c>
       <c r="M7" t="n">
-        <v>6.797</v>
+        <v>4.598</v>
       </c>
       <c r="N7" t="n">
-        <v>43</v>
+        <v>6562</v>
       </c>
       <c r="O7" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
         <v>42</v>
       </c>
       <c r="Q7" t="n">
+        <v>4.492</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T7" t="n">
+        <v>43</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X7" t="n">
         <v>42</v>
       </c>
-      <c r="R7" t="n">
+      <c r="Y7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB7" t="n">
         <v>0.7578</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AC7" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -902,33 +1136,63 @@
         <v>6.84</v>
       </c>
       <c r="J8" t="n">
+        <v>1819</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9</v>
+      </c>
+      <c r="L8" t="n">
         <v>69</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
+        <v>8.173999999999999</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10822</v>
+      </c>
+      <c r="O8" t="n">
+        <v>9</v>
+      </c>
+      <c r="P8" t="n">
         <v>69</v>
       </c>
-      <c r="L8" t="n">
-        <v>7499.44</v>
-      </c>
-      <c r="M8" t="n">
-        <v>10.416</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
+        <v>7.499</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T8" t="n">
         <v>69</v>
       </c>
-      <c r="O8" t="n">
+      <c r="U8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X8" t="n">
         <v>69</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Y8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z8" t="n">
         <v>67</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="AA8" t="n">
         <v>67</v>
       </c>
-      <c r="R8" t="n">
+      <c r="AB8" t="n">
         <v>0.5955</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AC8" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -963,37 +1227,79 @@
         <v>6.54</v>
       </c>
       <c r="J9" t="n">
+        <v>1019</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
         <v>44</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
+        <v>4.737</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6817</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
         <v>44</v>
       </c>
-      <c r="L9" t="n">
-        <v>4736.66</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8.359</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="Q9" t="n">
+        <v>4.737</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
         <v>43</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="AA9" t="n">
         <v>43</v>
       </c>
-      <c r="R9" t="n">
+      <c r="AB9" t="n">
         <v>0.7479</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AC9" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -1028,33 +1334,63 @@
         <v>6.93</v>
       </c>
       <c r="J10" t="n">
+        <v>2064</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" t="n">
         <v>78</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
+        <v>9.617000000000001</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12157</v>
+      </c>
+      <c r="O10" t="n">
+        <v>11</v>
+      </c>
+      <c r="P10" t="n">
         <v>79</v>
       </c>
-      <c r="L10" t="n">
-        <v>8661.08</v>
-      </c>
-      <c r="M10" t="n">
-        <v>12.673</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="Q10" t="n">
+        <v>8.661</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T10" t="n">
         <v>78</v>
       </c>
-      <c r="O10" t="n">
+      <c r="U10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X10" t="n">
         <v>79</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Y10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z10" t="n">
         <v>77</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="AA10" t="n">
         <v>77</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AB10" t="n">
         <v>0.5343</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AC10" t="n">
         <v>1.37</v>
       </c>
     </row>
@@ -1089,33 +1425,63 @@
         <v>7.23</v>
       </c>
       <c r="J11" t="n">
+        <v>5107</v>
+      </c>
+      <c r="K11" t="n">
+        <v>27</v>
+      </c>
+      <c r="L11" t="n">
         <v>154</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>20.882</v>
+      </c>
+      <c r="N11" t="n">
+        <v>24464</v>
+      </c>
+      <c r="O11" t="n">
+        <v>27</v>
+      </c>
+      <c r="P11" t="n">
         <v>157</v>
       </c>
-      <c r="L11" t="n">
-        <v>17414.41</v>
-      </c>
-      <c r="M11" t="n">
-        <v>25.12</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
+        <v>17.414</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T11" t="n">
         <v>154</v>
       </c>
-      <c r="O11" t="n">
+      <c r="U11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="V11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X11" t="n">
         <v>157</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Y11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="Z11" t="n">
         <v>154</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="AA11" t="n">
         <v>154</v>
       </c>
-      <c r="R11" t="n">
+      <c r="AB11" t="n">
         <v>0.1745</v>
       </c>
-      <c r="S11" t="n">
+      <c r="AC11" t="n">
         <v>3.17</v>
       </c>
     </row>
@@ -1150,33 +1516,63 @@
         <v>6.96</v>
       </c>
       <c r="J12" t="n">
+        <v>2424</v>
+      </c>
+      <c r="K12" t="n">
+        <v>81</v>
+      </c>
+      <c r="L12" t="n">
         <v>22</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
+        <v>3.057</v>
+      </c>
+      <c r="N12" t="n">
+        <v>482365</v>
+      </c>
+      <c r="O12" t="n">
+        <v>92</v>
+      </c>
+      <c r="P12" t="n">
         <v>9</v>
       </c>
-      <c r="L12" t="n">
-        <v>1436.81</v>
-      </c>
-      <c r="M12" t="n">
-        <v>503.462</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
+        <v>1.437</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T12" t="n">
         <v>22</v>
       </c>
-      <c r="O12" t="n">
+      <c r="U12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>451.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X12" t="n">
         <v>9</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Y12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z12" t="n">
         <v>24</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="AA12" t="n">
         <v>24</v>
       </c>
-      <c r="R12" t="n">
+      <c r="AB12" t="n">
         <v>0.4906</v>
       </c>
-      <c r="S12" t="n">
+      <c r="AC12" t="n">
         <v>3.22</v>
       </c>
     </row>
@@ -1211,33 +1607,63 @@
         <v>7.13</v>
       </c>
       <c r="J13" t="n">
+        <v>16985</v>
+      </c>
+      <c r="K13" t="n">
+        <v>227</v>
+      </c>
+      <c r="L13" t="n">
         <v>23</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
+        <v>3.186</v>
+      </c>
+      <c r="N13" t="n">
+        <v>420718</v>
+      </c>
+      <c r="O13" t="n">
+        <v>222</v>
+      </c>
+      <c r="P13" t="n">
         <v>12</v>
       </c>
-      <c r="L13" t="n">
-        <v>1722.65</v>
-      </c>
-      <c r="M13" t="n">
-        <v>424.801</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
+        <v>1.723</v>
+      </c>
+      <c r="R13" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="T13" t="n">
         <v>23</v>
       </c>
-      <c r="O13" t="n">
+      <c r="U13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>417.9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X13" t="n">
         <v>12</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Y13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z13" t="n">
         <v>29</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="AA13" t="n">
         <v>31</v>
       </c>
-      <c r="R13" t="n">
+      <c r="AB13" t="n">
         <v>0.171</v>
       </c>
-      <c r="S13" t="n">
+      <c r="AC13" t="n">
         <v>26.37</v>
       </c>
     </row>
@@ -1272,33 +1698,63 @@
         <v>8.68</v>
       </c>
       <c r="J14" t="n">
+        <v>5621</v>
+      </c>
+      <c r="K14" t="n">
+        <v>72</v>
+      </c>
+      <c r="L14" t="n">
         <v>158</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="N14" t="n">
+        <v>61873</v>
+      </c>
+      <c r="O14" t="n">
+        <v>57</v>
+      </c>
+      <c r="P14" t="n">
         <v>149</v>
       </c>
-      <c r="L14" t="n">
-        <v>15413.37</v>
-      </c>
-      <c r="M14" t="n">
-        <v>68.514</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="Q14" t="n">
+        <v>15.413</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T14" t="n">
         <v>158</v>
       </c>
-      <c r="O14" t="n">
+      <c r="U14" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="V14" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X14" t="n">
         <v>149</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Y14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z14" t="n">
         <v>95</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="AA14" t="n">
         <v>95</v>
       </c>
-      <c r="R14" t="n">
+      <c r="AB14" t="n">
         <v>0.3474</v>
       </c>
-      <c r="S14" t="n">
+      <c r="AC14" t="n">
         <v>4.51</v>
       </c>
     </row>
@@ -1333,33 +1789,63 @@
         <v>10.18</v>
       </c>
       <c r="J15" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K15" t="n">
+        <v>19</v>
+      </c>
+      <c r="L15" t="n">
         <v>68</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
+        <v>7.607</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8243</v>
+      </c>
+      <c r="O15" t="n">
+        <v>16</v>
+      </c>
+      <c r="P15" t="n">
         <v>54</v>
       </c>
-      <c r="L15" t="n">
-        <v>6167.63</v>
-      </c>
-      <c r="M15" t="n">
-        <v>8.474</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="Q15" t="n">
+        <v>6.168</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T15" t="n">
         <v>68</v>
       </c>
-      <c r="O15" t="n">
+      <c r="U15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X15" t="n">
         <v>54</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Y15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z15" t="n">
         <v>49</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="AA15" t="n">
         <v>45</v>
       </c>
-      <c r="R15" t="n">
+      <c r="AB15" t="n">
         <v>0.6929999999999999</v>
       </c>
-      <c r="S15" t="n">
+      <c r="AC15" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
@@ -1394,33 +1880,63 @@
         <v>51.07</v>
       </c>
       <c r="J16" t="n">
+        <v>7696</v>
+      </c>
+      <c r="K16" t="n">
+        <v>123</v>
+      </c>
+      <c r="L16" t="n">
         <v>184</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
+        <v>21.215</v>
+      </c>
+      <c r="N16" t="n">
+        <v>31011</v>
+      </c>
+      <c r="O16" t="n">
+        <v>89</v>
+      </c>
+      <c r="P16" t="n">
         <v>146</v>
       </c>
-      <c r="L16" t="n">
-        <v>17889.35</v>
-      </c>
-      <c r="M16" t="n">
-        <v>31.623</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="Q16" t="n">
+        <v>17.889</v>
+      </c>
+      <c r="R16" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T16" t="n">
         <v>185</v>
       </c>
-      <c r="O16" t="n">
+      <c r="U16" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="V16" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X16" t="n">
         <v>148</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Y16" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="Z16" t="n">
         <v>187</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="AA16" t="n">
         <v>200</v>
       </c>
-      <c r="R16" t="n">
+      <c r="AB16" t="n">
         <v>0.0833</v>
       </c>
-      <c r="S16" t="n">
+      <c r="AC16" t="n">
         <v>9.94</v>
       </c>
     </row>
@@ -1455,33 +1971,63 @@
         <v>72.75</v>
       </c>
       <c r="J17" t="n">
+        <v>15069</v>
+      </c>
+      <c r="K17" t="n">
+        <v>274</v>
+      </c>
+      <c r="L17" t="n">
         <v>383</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
+        <v>46.768</v>
+      </c>
+      <c r="N17" t="n">
+        <v>63536</v>
+      </c>
+      <c r="O17" t="n">
+        <v>197</v>
+      </c>
+      <c r="P17" t="n">
         <v>312</v>
       </c>
-      <c r="L17" t="n">
-        <v>39734.23</v>
-      </c>
-      <c r="M17" t="n">
-        <v>63.628</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="Q17" t="n">
+        <v>39.734</v>
+      </c>
+      <c r="R17" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T17" t="n">
         <v>434</v>
       </c>
-      <c r="O17" t="n">
+      <c r="U17" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X17" t="n">
         <v>284</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Y17" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="Z17" t="n">
         <v>407</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="AA17" t="n">
         <v>395</v>
       </c>
-      <c r="R17" t="n">
+      <c r="AB17" t="n">
         <v>0.0029</v>
       </c>
-      <c r="S17" t="n">
+      <c r="AC17" t="n">
         <v>32.43</v>
       </c>
     </row>
@@ -1516,33 +2062,63 @@
         <v>10.37</v>
       </c>
       <c r="J18" t="n">
+        <v>2671</v>
+      </c>
+      <c r="K18" t="n">
+        <v>30</v>
+      </c>
+      <c r="L18" t="n">
         <v>112</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
+        <v>12.151</v>
+      </c>
+      <c r="N18" t="n">
+        <v>14007</v>
+      </c>
+      <c r="O18" t="n">
+        <v>19</v>
+      </c>
+      <c r="P18" t="n">
         <v>81</v>
       </c>
-      <c r="L18" t="n">
-        <v>9344.66</v>
-      </c>
-      <c r="M18" t="n">
-        <v>14.506</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="Q18" t="n">
+        <v>9.345000000000001</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T18" t="n">
         <v>112</v>
       </c>
-      <c r="O18" t="n">
+      <c r="U18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X18" t="n">
         <v>81</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Y18" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="Z18" t="n">
         <v>69</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="AA18" t="n">
         <v>64</v>
       </c>
-      <c r="R18" t="n">
+      <c r="AB18" t="n">
         <v>0.519</v>
       </c>
-      <c r="S18" t="n">
+      <c r="AC18" t="n">
         <v>1.73</v>
       </c>
     </row>
@@ -1577,33 +2153,63 @@
         <v>8.52</v>
       </c>
       <c r="J19" t="n">
+        <v>4235</v>
+      </c>
+      <c r="K19" t="n">
+        <v>55</v>
+      </c>
+      <c r="L19" t="n">
         <v>127</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="N19" t="n">
+        <v>26640</v>
+      </c>
+      <c r="O19" t="n">
+        <v>47</v>
+      </c>
+      <c r="P19" t="n">
         <v>121</v>
       </c>
-      <c r="L19" t="n">
-        <v>12217.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>27.006</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="Q19" t="n">
+        <v>12.217</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="T19" t="n">
         <v>127</v>
       </c>
-      <c r="O19" t="n">
+      <c r="U19" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X19" t="n">
         <v>121</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Y19" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="Z19" t="n">
         <v>73</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="AA19" t="n">
         <v>73</v>
       </c>
-      <c r="R19" t="n">
+      <c r="AB19" t="n">
         <v>0.4557</v>
       </c>
-      <c r="S19" t="n">
+      <c r="AC19" t="n">
         <v>2.62</v>
       </c>
     </row>
@@ -1638,39 +2244,69 @@
         <v>6.66</v>
       </c>
       <c r="J20" t="n">
+        <v>2739</v>
+      </c>
+      <c r="K20" t="n">
+        <v>19</v>
+      </c>
+      <c r="L20" t="n">
         <v>73</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
+        <v>8.321</v>
+      </c>
+      <c r="N20" t="n">
+        <v>11356</v>
+      </c>
+      <c r="O20" t="n">
+        <v>16</v>
+      </c>
+      <c r="P20" t="n">
         <v>62</v>
       </c>
-      <c r="L20" t="n">
-        <v>6722.64</v>
-      </c>
-      <c r="M20" t="n">
-        <v>11.853</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="Q20" t="n">
+        <v>6.723</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T20" t="n">
         <v>73</v>
       </c>
-      <c r="O20" t="n">
+      <c r="U20" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="V20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X20" t="n">
         <v>62</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Y20" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Z20" t="n">
         <v>79</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="AA20" t="n">
         <v>75</v>
       </c>
-      <c r="R20" t="n">
+      <c r="AB20" t="n">
         <v>0.513</v>
       </c>
-      <c r="S20" t="n">
+      <c r="AC20" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:AC1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ZAC_zzx/results/fourway/四方法对比_论文对齐.xlsx
+++ b/ZAC_zzx/results/fourway/四方法对比_论文对齐.xlsx
@@ -649,10 +649,10 @@
         <v>5.09</v>
       </c>
       <c r="J3" t="n">
-        <v>605</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>26</v>
@@ -661,10 +661,10 @@
         <v>2.782</v>
       </c>
       <c r="N3" t="n">
-        <v>3899</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>26</v>
@@ -756,10 +756,10 @@
         <v>5.3</v>
       </c>
       <c r="J4" t="n">
-        <v>979</v>
+        <v>0.98</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>0.01</v>
       </c>
       <c r="L4" t="n">
         <v>37</v>
@@ -768,10 +768,10 @@
         <v>3.915</v>
       </c>
       <c r="N4" t="n">
-        <v>5319</v>
+        <v>5.32</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
       <c r="P4" t="n">
         <v>36</v>
@@ -863,10 +863,10 @@
         <v>3.47</v>
       </c>
       <c r="J5" t="n">
-        <v>998</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>0.01</v>
       </c>
       <c r="L5" t="n">
         <v>37</v>
@@ -875,10 +875,10 @@
         <v>4.267</v>
       </c>
       <c r="N5" t="n">
-        <v>5556</v>
+        <v>5.56</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
       <c r="P5" t="n">
         <v>36</v>
@@ -954,10 +954,10 @@
         <v>3.05</v>
       </c>
       <c r="J6" t="n">
-        <v>3193</v>
+        <v>3.19</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>0.01</v>
       </c>
       <c r="L6" t="n">
         <v>73</v>
@@ -966,10 +966,10 @@
         <v>11.029</v>
       </c>
       <c r="N6" t="n">
-        <v>11973</v>
+        <v>11.97</v>
       </c>
       <c r="O6" t="n">
-        <v>16</v>
+        <v>0.02</v>
       </c>
       <c r="P6" t="n">
         <v>76</v>
@@ -1045,10 +1045,10 @@
         <v>6.56</v>
       </c>
       <c r="J7" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>0.01</v>
       </c>
       <c r="L7" t="n">
         <v>43</v>
@@ -1057,10 +1057,10 @@
         <v>4.598</v>
       </c>
       <c r="N7" t="n">
-        <v>6562</v>
+        <v>6.56</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
       <c r="P7" t="n">
         <v>42</v>
@@ -1136,10 +1136,10 @@
         <v>6.84</v>
       </c>
       <c r="J8" t="n">
-        <v>1819</v>
+        <v>1.82</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>0.01</v>
       </c>
       <c r="L8" t="n">
         <v>69</v>
@@ -1148,10 +1148,10 @@
         <v>8.173999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>10822</v>
+        <v>10.82</v>
       </c>
       <c r="O8" t="n">
-        <v>9</v>
+        <v>0.01</v>
       </c>
       <c r="P8" t="n">
         <v>69</v>
@@ -1227,10 +1227,10 @@
         <v>6.54</v>
       </c>
       <c r="J9" t="n">
-        <v>1019</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>0.01</v>
       </c>
       <c r="L9" t="n">
         <v>44</v>
@@ -1239,10 +1239,10 @@
         <v>4.737</v>
       </c>
       <c r="N9" t="n">
-        <v>6817</v>
+        <v>6.82</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
       <c r="P9" t="n">
         <v>44</v>
@@ -1334,10 +1334,10 @@
         <v>6.93</v>
       </c>
       <c r="J10" t="n">
-        <v>2064</v>
+        <v>2.06</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>0.01</v>
       </c>
       <c r="L10" t="n">
         <v>78</v>
@@ -1346,10 +1346,10 @@
         <v>9.617000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>12157</v>
+        <v>12.16</v>
       </c>
       <c r="O10" t="n">
-        <v>11</v>
+        <v>0.01</v>
       </c>
       <c r="P10" t="n">
         <v>79</v>
@@ -1425,10 +1425,10 @@
         <v>7.23</v>
       </c>
       <c r="J11" t="n">
-        <v>5107</v>
+        <v>5.11</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>0.03</v>
       </c>
       <c r="L11" t="n">
         <v>154</v>
@@ -1437,10 +1437,10 @@
         <v>20.882</v>
       </c>
       <c r="N11" t="n">
-        <v>24464</v>
+        <v>24.46</v>
       </c>
       <c r="O11" t="n">
-        <v>27</v>
+        <v>0.03</v>
       </c>
       <c r="P11" t="n">
         <v>157</v>
@@ -1516,10 +1516,10 @@
         <v>6.96</v>
       </c>
       <c r="J12" t="n">
-        <v>2424</v>
+        <v>2.42</v>
       </c>
       <c r="K12" t="n">
-        <v>81</v>
+        <v>0.08</v>
       </c>
       <c r="L12" t="n">
         <v>22</v>
@@ -1528,10 +1528,10 @@
         <v>3.057</v>
       </c>
       <c r="N12" t="n">
-        <v>482365</v>
+        <v>482.37</v>
       </c>
       <c r="O12" t="n">
-        <v>92</v>
+        <v>0.09</v>
       </c>
       <c r="P12" t="n">
         <v>9</v>
@@ -1607,10 +1607,10 @@
         <v>7.13</v>
       </c>
       <c r="J13" t="n">
-        <v>16985</v>
+        <v>16.98</v>
       </c>
       <c r="K13" t="n">
-        <v>227</v>
+        <v>0.23</v>
       </c>
       <c r="L13" t="n">
         <v>23</v>
@@ -1619,10 +1619,10 @@
         <v>3.186</v>
       </c>
       <c r="N13" t="n">
-        <v>420718</v>
+        <v>420.72</v>
       </c>
       <c r="O13" t="n">
-        <v>222</v>
+        <v>0.22</v>
       </c>
       <c r="P13" t="n">
         <v>12</v>
@@ -1698,10 +1698,10 @@
         <v>8.68</v>
       </c>
       <c r="J14" t="n">
-        <v>5621</v>
+        <v>5.62</v>
       </c>
       <c r="K14" t="n">
-        <v>72</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>158</v>
@@ -1710,10 +1710,10 @@
         <v>16.66</v>
       </c>
       <c r="N14" t="n">
-        <v>61873</v>
+        <v>61.87</v>
       </c>
       <c r="O14" t="n">
-        <v>57</v>
+        <v>0.06</v>
       </c>
       <c r="P14" t="n">
         <v>149</v>
@@ -1789,10 +1789,10 @@
         <v>10.18</v>
       </c>
       <c r="J15" t="n">
-        <v>1520</v>
+        <v>1.52</v>
       </c>
       <c r="K15" t="n">
-        <v>19</v>
+        <v>0.02</v>
       </c>
       <c r="L15" t="n">
         <v>68</v>
@@ -1801,10 +1801,10 @@
         <v>7.607</v>
       </c>
       <c r="N15" t="n">
-        <v>8243</v>
+        <v>8.24</v>
       </c>
       <c r="O15" t="n">
-        <v>16</v>
+        <v>0.02</v>
       </c>
       <c r="P15" t="n">
         <v>54</v>
@@ -1880,10 +1880,10 @@
         <v>51.07</v>
       </c>
       <c r="J16" t="n">
-        <v>7696</v>
+        <v>7.7</v>
       </c>
       <c r="K16" t="n">
-        <v>123</v>
+        <v>0.12</v>
       </c>
       <c r="L16" t="n">
         <v>184</v>
@@ -1892,10 +1892,10 @@
         <v>21.215</v>
       </c>
       <c r="N16" t="n">
-        <v>31011</v>
+        <v>31.01</v>
       </c>
       <c r="O16" t="n">
-        <v>89</v>
+        <v>0.09</v>
       </c>
       <c r="P16" t="n">
         <v>146</v>
@@ -1971,10 +1971,10 @@
         <v>72.75</v>
       </c>
       <c r="J17" t="n">
-        <v>15069</v>
+        <v>15.07</v>
       </c>
       <c r="K17" t="n">
-        <v>274</v>
+        <v>0.27</v>
       </c>
       <c r="L17" t="n">
         <v>383</v>
@@ -1983,10 +1983,10 @@
         <v>46.768</v>
       </c>
       <c r="N17" t="n">
-        <v>63536</v>
+        <v>63.54</v>
       </c>
       <c r="O17" t="n">
-        <v>197</v>
+        <v>0.2</v>
       </c>
       <c r="P17" t="n">
         <v>312</v>
@@ -2062,10 +2062,10 @@
         <v>10.37</v>
       </c>
       <c r="J18" t="n">
-        <v>2671</v>
+        <v>2.67</v>
       </c>
       <c r="K18" t="n">
-        <v>30</v>
+        <v>0.03</v>
       </c>
       <c r="L18" t="n">
         <v>112</v>
@@ -2074,10 +2074,10 @@
         <v>12.151</v>
       </c>
       <c r="N18" t="n">
-        <v>14007</v>
+        <v>14.01</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>0.02</v>
       </c>
       <c r="P18" t="n">
         <v>81</v>
@@ -2153,10 +2153,10 @@
         <v>8.52</v>
       </c>
       <c r="J19" t="n">
-        <v>4235</v>
+        <v>4.24</v>
       </c>
       <c r="K19" t="n">
-        <v>55</v>
+        <v>0.06</v>
       </c>
       <c r="L19" t="n">
         <v>127</v>
@@ -2165,10 +2165,10 @@
         <v>13.37</v>
       </c>
       <c r="N19" t="n">
-        <v>26640</v>
+        <v>26.64</v>
       </c>
       <c r="O19" t="n">
-        <v>47</v>
+        <v>0.05</v>
       </c>
       <c r="P19" t="n">
         <v>121</v>
@@ -2244,10 +2244,10 @@
         <v>6.66</v>
       </c>
       <c r="J20" t="n">
-        <v>2739</v>
+        <v>2.74</v>
       </c>
       <c r="K20" t="n">
-        <v>19</v>
+        <v>0.02</v>
       </c>
       <c r="L20" t="n">
         <v>73</v>
@@ -2256,10 +2256,10 @@
         <v>8.321</v>
       </c>
       <c r="N20" t="n">
-        <v>11356</v>
+        <v>11.36</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>0.02</v>
       </c>
       <c r="P20" t="n">
         <v>62</v>
